--- a/cuadros/JUNIO/NAGUANAGUA.xlsx
+++ b/cuadros/JUNIO/NAGUANAGUA.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +413,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="53.61328125" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -479,12 +481,12 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
         </is>
       </c>
     </row>
@@ -547,14 +549,9 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>INC_132032_0.png INC_132032_1.png INC_132032_2.png</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ID_20260603132032</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/NAGUANAGUA.xlsx
+++ b/cuadros/JUNIO/NAGUANAGUA.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,11 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,11 +420,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="53.61328125" customWidth="1" min="13" max="13"/>
-  </cols>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -552,6 +557,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_132032_0.png INC_132032_1.png INC_132032_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>001111</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RECIBIDOR FELIX RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SE RECIBE 189.8KG DE PARCHITA, EN FACTURA 190KG. DIFERENCIA: 200GR FALTANTES</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260606115642</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>INC_115642_0.png INC_115642_1.png INC_115642_2.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/NAGUANAGUA.xlsx
+++ b/cuadros/JUNIO/NAGUANAGUA.xlsx
@@ -607,11 +607,11 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_121040_0.jpeg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">

--- a/cuadros/JUNIO/NAGUANAGUA.xlsx
+++ b/cuadros/JUNIO/NAGUANAGUA.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +634,76 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_115642_0.png INC_115642_1.png INC_115642_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAGUANAGUA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13864</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SUB STEVEN J. SERVET</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INGRESA TARA DE CESTAS ERRONEAS, INGRESA CESTAS DE 2.6KG C/U, SE VISUALIZA Y VERIFICA CESTAS DE 2.3KG C/U. DIFFERENCIA DE 600GR</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260606122446</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_122446_0.png INC_122446_1.png INC_122446_2.png</t>
         </is>
       </c>
     </row>
